--- a/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -488,31 +488,27 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>0.544747980369836</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08949596073967192</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.196585532585614</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.304</v>
+        <v>0.001</v>
       </c>
       <c r="H2" t="n">
-        <v>139.1285754717651</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>255.3998922167808</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6.608072522812817</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>21.96785730463685</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +519,27 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2428147097433156</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1357779353850268</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6413614022031565</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.916</v>
+        <v>0.001</v>
       </c>
       <c r="H3" t="n">
-        <v>83.01890717491537</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>341.9022976930696</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.179122234496873</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>10.95656751750038</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +550,27 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2569693316162575</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.008398764235079126</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9683505124904532</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.575</v>
+        <v>0.001</v>
       </c>
       <c r="H4" t="n">
-        <v>129.3408161842689</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>503.3317220026033</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.203440897559276</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>14.15770357808967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +581,27 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2085107149153909</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002240609457571097</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.001075733569514</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.463</v>
+        <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>117.3508446474798</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>562.8048644651101</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.229932970664012</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>12.14632198591099</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +612,27 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>0.205866393865575</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04042189258756979</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.244322974020434</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.139</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>137.439840199558</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>667.6166887602958</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.360467161313176</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13.54535484617452</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +643,27 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1873924089280926</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04228391052239466</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.29139513527441</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.099</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>156.5262088076471</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>835.2857498497199</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.997295431289754</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>14.44811206083668</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +674,27 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1770260346242412</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05233300956730791</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.419694762745659</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>164.7800358829591</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>930.8237414498062</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.392532869663265</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16.24256966322634</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +705,27 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1418517828072764</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02893754370297064</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.25627895943433</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.151</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>143.0650718572631</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1008.553216787096</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.039275644744853</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>13.65340723898973</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +736,27 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1260483968276754</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02200653930716046</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.211516209260501</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.192</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>137.5014964690407</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1090.86271566804</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.875773920897301</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>12.32894418029447</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +767,27 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1195329227728079</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02586621242948961</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.27615160535351</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.117</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>141.3445593048543</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1182.473882726879</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.812972526800572</v>
-      </c>
+        <v>20.36872504666393</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>12.85097974840304</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +801,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1167078069164825</v>
+        <v>0.01284365820971448</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03177586527383636</v>
+        <v>-0.004784133607969254</v>
       </c>
       <c r="F12" t="n">
-        <v>1.374133272585885</v>
+        <v>0.7286027848837033</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="H12" t="n">
-        <v>145.3679216240949</v>
+        <v>0.2650126748844602</v>
       </c>
       <c r="I12" t="n">
-        <v>1245.571530001605</v>
+        <v>20.63373772154839</v>
       </c>
       <c r="J12" t="n">
-        <v>1.750562567431439</v>
+        <v>0.004649345173411585</v>
       </c>
       <c r="K12" t="n">
-        <v>12.88612876584453</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +836,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1085997328666637</v>
+        <v>0.04315249398046656</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0290104233011873</v>
+        <v>0.02720503554680775</v>
       </c>
       <c r="F13" t="n">
-        <v>1.364501507295034</v>
+        <v>2.705916692617828</v>
       </c>
       <c r="G13" t="n">
-        <v>0.077</v>
+        <v>0.028</v>
       </c>
       <c r="H13" t="n">
-        <v>141.6332289272562</v>
+        <v>0.9698895486712799</v>
       </c>
       <c r="I13" t="n">
-        <v>1304.176586706251</v>
+        <v>22.47586313575088</v>
       </c>
       <c r="J13" t="n">
-        <v>1.545208983387515</v>
+        <v>0.01589982866674229</v>
       </c>
       <c r="K13" t="n">
-        <v>13.07643888021562</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +871,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.100238568162424</v>
+        <v>0.02158157294671699</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02648763112655705</v>
+        <v>0.006528981761281916</v>
       </c>
       <c r="F14" t="n">
-        <v>1.359149757157329</v>
+        <v>1.433744707529113</v>
       </c>
       <c r="G14" t="n">
-        <v>0.075</v>
+        <v>0.19</v>
       </c>
       <c r="H14" t="n">
-        <v>139.7116831041968</v>
+        <v>0.5281933097388927</v>
       </c>
       <c r="I14" t="n">
-        <v>1393.791687824307</v>
+        <v>24.47427307745156</v>
       </c>
       <c r="J14" t="n">
-        <v>1.246144435321775</v>
+        <v>0.008002928935437768</v>
       </c>
       <c r="K14" t="n">
-        <v>14.20549564751429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +906,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09611096008113519</v>
+        <v>0.01681744225711929</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02763451766303937</v>
+        <v>0.002771977146506788</v>
       </c>
       <c r="F15" t="n">
-        <v>1.403562403173804</v>
+        <v>1.197357447736796</v>
       </c>
       <c r="G15" t="n">
-        <v>0.043</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
-        <v>147.1630206111505</v>
+        <v>0.4286388328662348</v>
       </c>
       <c r="I15" t="n">
-        <v>1531.178343103825</v>
+        <v>25.48775410153586</v>
       </c>
       <c r="J15" t="n">
-        <v>1.222080294678339</v>
+        <v>0.00603716666008782</v>
       </c>
       <c r="K15" t="n">
-        <v>16.77578134024029</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +941,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0933619878341042</v>
+        <v>0.02296861074014419</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02860212982225452</v>
+        <v>0.009765483858254154</v>
       </c>
       <c r="F16" t="n">
-        <v>1.441664492485776</v>
+        <v>1.739634174965709</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05</v>
+        <v>0.126</v>
       </c>
       <c r="H16" t="n">
-        <v>147.3032737129005</v>
+        <v>0.6337176378618078</v>
       </c>
       <c r="I16" t="n">
-        <v>1577.764967629493</v>
+        <v>27.59059505302189</v>
       </c>
       <c r="J16" t="n">
-        <v>1.17663784374443</v>
+        <v>0.008449568504824109</v>
       </c>
       <c r="K16" t="n">
-        <v>19.24887439638324</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +976,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08829725269132459</v>
+        <v>0.03509486386490714</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02751706953741295</v>
+        <v>0.02288087479990586</v>
       </c>
       <c r="F17" t="n">
-        <v>1.452730941394703</v>
+        <v>2.873333493106722</v>
       </c>
       <c r="G17" t="n">
-        <v>0.038</v>
+        <v>0.024</v>
       </c>
       <c r="H17" t="n">
-        <v>155.4066757000799</v>
+        <v>1.042931354308237</v>
       </c>
       <c r="I17" t="n">
-        <v>1760.039762996488</v>
+        <v>29.71749251750506</v>
       </c>
       <c r="J17" t="n">
-        <v>0.902991279962726</v>
+        <v>0.01303664192885296</v>
       </c>
       <c r="K17" t="n">
-        <v>19.19904526911579</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1011,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08667308534827273</v>
+        <v>0.01664959133399989</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02959015318253977</v>
+        <v>0.004943038849880899</v>
       </c>
       <c r="F18" t="n">
-        <v>1.518371289979088</v>
+        <v>1.42224547804202</v>
       </c>
       <c r="G18" t="n">
-        <v>0.022</v>
+        <v>0.181</v>
       </c>
       <c r="H18" t="n">
-        <v>161.04208209533</v>
+        <v>0.5249411695533597</v>
       </c>
       <c r="I18" t="n">
-        <v>1858.040260690217</v>
+        <v>31.52877202946026</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8508867969286098</v>
+        <v>0.00617577846533364</v>
       </c>
       <c r="K18" t="n">
-        <v>23.94829948823562</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1046,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08758038722845418</v>
+        <v>0.01369231569883402</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03326969599205265</v>
+        <v>0.002484273831775186</v>
       </c>
       <c r="F19" t="n">
-        <v>1.612580971345726</v>
+        <v>1.221651012838985</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01</v>
+        <v>0.285</v>
       </c>
       <c r="H19" t="n">
-        <v>165.5041669544819</v>
+        <v>0.462054235293281</v>
       </c>
       <c r="I19" t="n">
-        <v>1889.740068432935</v>
+        <v>33.74551430570855</v>
       </c>
       <c r="J19" t="n">
-        <v>0.826704934753105</v>
+        <v>0.005191620621272821</v>
       </c>
       <c r="K19" t="n">
-        <v>24.88178074589872</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1081,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1002932046883541</v>
+        <v>0.01317990005032397</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04974787910904821</v>
+        <v>0.002568931233660865</v>
       </c>
       <c r="F20" t="n">
-        <v>1.984223141089347</v>
+        <v>1.242101478012696</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.266</v>
       </c>
       <c r="H20" t="n">
-        <v>205.5002529712815</v>
+        <v>0.4634471397395242</v>
       </c>
       <c r="I20" t="n">
-        <v>2048.994780950935</v>
+        <v>35.16317559085985</v>
       </c>
       <c r="J20" t="n">
-        <v>0.924773258345834</v>
+        <v>0.004930288720633234</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38080000515973</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1116,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09364920780836127</v>
+        <v>0.03054585359786723</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04543905928752956</v>
+        <v>0.02065346434886595</v>
       </c>
       <c r="F21" t="n">
-        <v>1.942520624426099</v>
+        <v>3.08781355332847</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="H21" t="n">
-        <v>202.2198535514442</v>
+        <v>1.10787403471876</v>
       </c>
       <c r="I21" t="n">
-        <v>2159.333306537479</v>
+        <v>36.26921183162201</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8923151424009118</v>
+        <v>0.011190646815341</v>
       </c>
       <c r="K21" t="n">
-        <v>24.66664615173071</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1148,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>233</v>
       </c>
       <c r="D22" t="n">
-        <v>0.09439309903001616</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04818866530705779</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F22" t="n">
-        <v>2.042944614276562</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H22" t="n">
-        <v>209.2542810445551</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I22" t="n">
-        <v>2216.838764643315</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J22" t="n">
-        <v>0.826649140837354</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K22" t="n">
-        <v>23.88524951551354</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1183,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08816854498512472</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04390488212032495</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F23" t="n">
-        <v>1.991894463285366</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H23" t="n">
-        <v>205.7237906059632</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I23" t="n">
-        <v>2333.301413113619</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6296333991008448</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K23" t="n">
-        <v>4.147892223809977</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1218,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09442469685716871</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05249991430425982</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F24" t="n">
-        <v>2.252240586770014</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H24" t="n">
-        <v>235.3006778370766</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I24" t="n">
-        <v>2491.93998677066</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J24" t="n">
-        <v>1.002948898152862</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K24" t="n">
-        <v>2.517119212399473</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1253,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08716267680616355</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04641101059215291</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F25" t="n">
-        <v>2.138873938268485</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H25" t="n">
-        <v>234.1612553598748</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I25" t="n">
-        <v>2686.485362084663</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J25" t="n">
-        <v>1.107673508680064</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K25" t="n">
-        <v>1.800938813288458</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1288,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08621983852181925</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04716940427061489</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F26" t="n">
-        <v>2.207909852351008</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G26" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H26" t="n">
-        <v>242.8060195499113</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I26" t="n">
-        <v>2816.127050486943</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J26" t="n">
-        <v>1.034984151079228</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K26" t="n">
-        <v>1.596579074313268</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1323,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08929192471863638</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0519678232726789</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F27" t="n">
-        <v>2.392339567716702</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H27" t="n">
-        <v>259.2331212450961</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I27" t="n">
-        <v>2903.209019874456</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J27" t="n">
-        <v>1.198039602967755</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K27" t="n">
-        <v>1.379256177242862</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1358,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08620861150106385</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04994704846539166</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F28" t="n">
-        <v>2.377410246112576</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>258.4741360261601</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I28" t="n">
-        <v>2998.240332672223</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J28" t="n">
-        <v>1.174148866116118</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K28" t="n">
-        <v>1.315775277965552</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1393,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="D29" t="n">
-        <v>0.09461217045763831</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06005538307052538</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F29" t="n">
-        <v>2.737875179129678</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>303.0903122762216</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I29" t="n">
-        <v>3203.502369834411</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J29" t="n">
-        <v>1.40443694048454</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K29" t="n">
-        <v>1.37858423642228</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1428,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1012280367121461</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E30" t="n">
-        <v>0.06818494982656309</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F30" t="n">
-        <v>3.063516343453772</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="n">
-        <v>341.781200855171</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I30" t="n">
-        <v>3376.349200835202</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J30" t="n">
-        <v>1.646291783726154</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K30" t="n">
-        <v>1.349731857653184</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1463,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1069428568823294</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E31" t="n">
-        <v>0.07504795891384108</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F31" t="n">
-        <v>3.352976924020503</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G31" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H31" t="n">
-        <v>371.6328881506691</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I31" t="n">
-        <v>3475.060410622669</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J31" t="n">
-        <v>1.742870098514709</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K31" t="n">
-        <v>1.339992638408889</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1498,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1102614658163132</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07958082670653088</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F32" t="n">
-        <v>3.593845141940253</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G32" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H32" t="n">
-        <v>403.2838699926373</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I32" t="n">
-        <v>3657.523206379969</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J32" t="n">
-        <v>1.756800865695149</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K32" t="n">
-        <v>1.318774584884015</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1533,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1150056890558954</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08550587869109183</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F33" t="n">
-        <v>3.898522995019309</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>440.0943406732555</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I33" t="n">
-        <v>3826.718002266476</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J33" t="n">
-        <v>1.822454780783953</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K33" t="n">
-        <v>1.320586106432624</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1568,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1222064025208484</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0937066103949018</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F34" t="n">
-        <v>4.287975223847001</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H34" t="n">
-        <v>494.1378486790975</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I34" t="n">
-        <v>4043.469396742922</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J34" t="n">
-        <v>1.864520868985286</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K34" t="n">
-        <v>1.310743609949564</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1603,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1124390656066493</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08452834439931123</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F35" t="n">
-        <v>4.028525983667084</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G35" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H35" t="n">
-        <v>467.5737672765769</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I35" t="n">
-        <v>4158.463650990408</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J35" t="n">
-        <v>1.630666122753286</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K35" t="n">
-        <v>1.281132572779226</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1638,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1098877876648942</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08275022021565315</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F36" t="n">
-        <v>4.049286579220182</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G36" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>470.6118484610674</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I36" t="n">
-        <v>4282.658323199764</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J36" t="n">
-        <v>1.535147210310985</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K36" t="n">
-        <v>1.274105081187802</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1673,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1048232825108793</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07818111829989371</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F37" t="n">
-        <v>3.9344882675731</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G37" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H37" t="n">
-        <v>455.9926369715731</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I37" t="n">
-        <v>4350.10835426039</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J37" t="n">
-        <v>1.4015829267882</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K37" t="n">
-        <v>1.260752482436434</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1708,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1023269110750668</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E38" t="n">
-        <v>0.07638260214660053</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F38" t="n">
-        <v>3.944098544201077</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G38" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H38" t="n">
-        <v>457.7757896558662</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I38" t="n">
-        <v>4473.659810956697</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J38" t="n">
-        <v>1.308921726591947</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K38" t="n">
-        <v>1.222888043805851</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1743,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1003052136384607</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E39" t="n">
-        <v>0.075032888178867</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F39" t="n">
-        <v>3.968974434063534</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G39" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H39" t="n">
-        <v>464.7435217887124</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I39" t="n">
-        <v>4633.293773380814</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J39" t="n">
-        <v>1.185920472526337</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K39" t="n">
-        <v>1.190164484130783</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1778,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>233</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09642419203852903</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0716006808307964</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F40" t="n">
-        <v>3.884389731638453</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G40" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H40" t="n">
-        <v>454.1394840340457</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I40" t="n">
-        <v>4709.808549420683</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J40" t="n">
-        <v>1.189628559778527</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K40" t="n">
-        <v>1.16349121470578</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1813,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1000033647509839</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07593928359459301</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F41" t="n">
-        <v>4.155710916243548</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H41" t="n">
-        <v>489.7449940592434</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I41" t="n">
-        <v>4897.285159141857</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J41" t="n">
-        <v>1.150410460585756</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K41" t="n">
-        <v>1.120148884567708</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1848,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1013803251323797</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E42" t="n">
-        <v>0.07797877109936868</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F42" t="n">
-        <v>4.332204818080436</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H42" t="n">
-        <v>513.0922402792889</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I42" t="n">
-        <v>5061.063274450018</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J42" t="n">
-        <v>1.137141335632057</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K42" t="n">
-        <v>1.078998194105045</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1883,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09320081515269533</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E43" t="n">
-        <v>0.07006818288618244</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F43" t="n">
-        <v>4.028975781005872</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H43" t="n">
-        <v>480.3501061746566</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I43" t="n">
-        <v>5153.926018647757</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J43" t="n">
-        <v>1.109167694885819</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K43" t="n">
-        <v>1.060954735343781</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1918,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09945963871782476</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E44" t="n">
-        <v>0.07705813719339261</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F44" t="n">
-        <v>4.439864828228099</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G44" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H44" t="n">
-        <v>530.9400710245059</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I44" t="n">
-        <v>5338.246527627422</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J44" t="n">
-        <v>1.241617411384147</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K44" t="n">
-        <v>1.045976719372852</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1953,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1034121287368099</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08165028720129563</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F45" t="n">
-        <v>4.751993463790557</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G45" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H45" t="n">
-        <v>564.3814174544046</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I45" t="n">
-        <v>5457.594039967878</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J45" t="n">
-        <v>1.365113021484189</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K45" t="n">
-        <v>1.045775383405648</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +1988,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1034799312482162</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08213421532555476</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F46" t="n">
-        <v>4.847807945310351</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G46" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H46" t="n">
-        <v>578.8421393743342</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I46" t="n">
-        <v>5593.762311127477</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J46" t="n">
-        <v>1.403171281002232</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K46" t="n">
-        <v>1.030515750974158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2023,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1002141400886821</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07928888753260488</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F47" t="n">
-        <v>4.789148413865987</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G47" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H47" t="n">
-        <v>576.7694346715055</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I47" t="n">
-        <v>5755.369792736903</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J47" t="n">
-        <v>1.483164757261752</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K47" t="n">
-        <v>1.014023381533394</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2058,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09874169752347479</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07825855428537198</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F48" t="n">
-        <v>4.820632086377983</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H48" t="n">
-        <v>583.6457550033526</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I48" t="n">
-        <v>5910.833717078816</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J48" t="n">
-        <v>1.461139203118333</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K48" t="n">
-        <v>1.006775722777937</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2093,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D49" t="n">
-        <v>0.09792401334069677</v>
+        <v>0.01913364870431505</v>
       </c>
       <c r="E49" t="n">
-        <v>0.07778838863848014</v>
+        <v>0.01488747402338131</v>
       </c>
       <c r="F49" t="n">
-        <v>4.863222015153918</v>
+        <v>4.506090809271114</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H49" t="n">
-        <v>588.5525626368674</v>
+        <v>2.026348644764353</v>
       </c>
       <c r="I49" t="n">
-        <v>6010.298623986928</v>
+        <v>105.9049779829692</v>
       </c>
       <c r="J49" t="n">
-        <v>1.456644441675161</v>
+        <v>0.008734261399846356</v>
       </c>
       <c r="K49" t="n">
-        <v>1.001277893132821</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -504,7 +504,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>20.36872504666393</v>
+        <v>1193.756239308613</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
@@ -801,25 +801,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01284365820971448</v>
+        <v>0.02269091255701996</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.004784133607969254</v>
+        <v>0.005238964566966819</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7286027848837033</v>
+        <v>1.300193684392866</v>
       </c>
       <c r="G12" t="n">
-        <v>0.455</v>
+        <v>0.23</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2650126748844602</v>
+        <v>27.71632719738638</v>
       </c>
       <c r="I12" t="n">
-        <v>20.63373772154839</v>
+        <v>1221.472566506</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004649345173411585</v>
+        <v>0.4862513543401121</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -836,25 +836,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04315249398046656</v>
+        <v>0.02453033892644999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02720503554680775</v>
+        <v>0.008272511241890879</v>
       </c>
       <c r="F13" t="n">
-        <v>2.705916692617828</v>
+        <v>1.50883250840133</v>
       </c>
       <c r="G13" t="n">
-        <v>0.028</v>
+        <v>0.126</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9698895486712799</v>
+        <v>32.45789024453138</v>
       </c>
       <c r="I13" t="n">
-        <v>22.47586313575088</v>
+        <v>1323.17333004859</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01589982866674229</v>
+        <v>0.5320965613857604</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -871,25 +871,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02158157294671699</v>
+        <v>0.01620875000947223</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006528981761281916</v>
+        <v>0.001073500009617923</v>
       </c>
       <c r="F14" t="n">
-        <v>1.433744707529113</v>
+        <v>1.070927140921246</v>
       </c>
       <c r="G14" t="n">
-        <v>0.19</v>
+        <v>0.351</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5281933097388927</v>
+        <v>23.367298642189</v>
       </c>
       <c r="I14" t="n">
-        <v>24.47427307745156</v>
+        <v>1441.647173812502</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008002928935437768</v>
+        <v>0.354049979427106</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -906,25 +906,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01681744225711929</v>
+        <v>0.01460547295425601</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002771977146506788</v>
+        <v>0.0005284082821739311</v>
       </c>
       <c r="F15" t="n">
-        <v>1.197357447736796</v>
+        <v>1.037536822802406</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>0.349</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4286388328662348</v>
+        <v>22.56871389911598</v>
       </c>
       <c r="I15" t="n">
-        <v>25.48775410153586</v>
+        <v>1545.223079718175</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00603716666008782</v>
+        <v>0.3178692098467041</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -941,25 +941,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02296861074014419</v>
+        <v>0.01247551195550653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.009765483858254154</v>
+        <v>-0.0008694135586082563</v>
       </c>
       <c r="F16" t="n">
-        <v>1.739634174965709</v>
+        <v>0.9348506248544681</v>
       </c>
       <c r="G16" t="n">
-        <v>0.126</v>
+        <v>0.468</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6337176378618078</v>
+        <v>20.33865913189402</v>
       </c>
       <c r="I16" t="n">
-        <v>27.59059505302189</v>
+        <v>1630.286532883871</v>
       </c>
       <c r="J16" t="n">
-        <v>0.008449568504824109</v>
+        <v>0.271182121758587</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -976,25 +976,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03509486386490714</v>
+        <v>0.01650073871402433</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02288087479990586</v>
+        <v>0.004051380976227148</v>
       </c>
       <c r="F17" t="n">
-        <v>2.873333493106722</v>
+        <v>1.325428914611946</v>
       </c>
       <c r="G17" t="n">
-        <v>0.024</v>
+        <v>0.205</v>
       </c>
       <c r="H17" t="n">
-        <v>1.042931354308237</v>
+        <v>28.33363958879021</v>
       </c>
       <c r="I17" t="n">
-        <v>29.71749251750506</v>
+        <v>1717.113402002351</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01303664192885296</v>
+        <v>0.3541704948598777</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1011,25 +1011,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01664959133399989</v>
+        <v>0.01372764539297056</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004943038849880899</v>
+        <v>0.001986307838125034</v>
       </c>
       <c r="F18" t="n">
-        <v>1.42224547804202</v>
+        <v>1.169172194296146</v>
       </c>
       <c r="G18" t="n">
-        <v>0.181</v>
+        <v>0.267</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5249411695533597</v>
+        <v>24.89531983682641</v>
       </c>
       <c r="I18" t="n">
-        <v>31.52877202946026</v>
+        <v>1813.517112670642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00617577846533364</v>
+        <v>0.2928861157273693</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -1046,25 +1046,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01369231569883402</v>
+        <v>0.01250334781456195</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002484273831775186</v>
+        <v>0.001281794948818304</v>
       </c>
       <c r="F19" t="n">
-        <v>1.221651012838985</v>
+        <v>1.114226164966108</v>
       </c>
       <c r="G19" t="n">
-        <v>0.285</v>
+        <v>0.326</v>
       </c>
       <c r="H19" t="n">
-        <v>0.462054235293281</v>
+        <v>24.23803397751677</v>
       </c>
       <c r="I19" t="n">
-        <v>33.74551430570855</v>
+        <v>1938.523532816395</v>
       </c>
       <c r="J19" t="n">
-        <v>0.005191620621272821</v>
+        <v>0.2723374604215367</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1081,25 +1081,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01317990005032397</v>
+        <v>0.006237432351329804</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002568931233660865</v>
+        <v>-0.00444818665564517</v>
       </c>
       <c r="F20" t="n">
-        <v>1.242101478012696</v>
+        <v>0.5837221360090018</v>
       </c>
       <c r="G20" t="n">
-        <v>0.266</v>
+        <v>0.82</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4634471397395242</v>
+        <v>12.82406472187948</v>
       </c>
       <c r="I20" t="n">
-        <v>35.16317559085985</v>
+        <v>2055.984578196735</v>
       </c>
       <c r="J20" t="n">
-        <v>0.004930288720633234</v>
+        <v>0.1364262204455263</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1116,25 +1116,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03054585359786723</v>
+        <v>0.0102538231992958</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02065346434886595</v>
+        <v>0.0001543724156152226</v>
       </c>
       <c r="F21" t="n">
-        <v>3.08781355332847</v>
+        <v>1.015285228763587</v>
       </c>
       <c r="G21" t="n">
-        <v>0.013</v>
+        <v>0.401</v>
       </c>
       <c r="H21" t="n">
-        <v>1.10787403471876</v>
+        <v>21.87719381121574</v>
       </c>
       <c r="I21" t="n">
-        <v>36.26921183162201</v>
+        <v>2133.564562798214</v>
       </c>
       <c r="J21" t="n">
-        <v>0.011190646815341</v>
+        <v>0.220981755668846</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1151,25 +1151,25 @@
         <v>233</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F22" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G22" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I22" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J22" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1186,25 +1186,25 @@
         <v>233</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F23" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I23" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J23" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1221,25 +1221,25 @@
         <v>233</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F24" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I24" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J24" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1256,25 +1256,25 @@
         <v>233</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F25" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I25" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J25" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1291,25 +1291,25 @@
         <v>233</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F26" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I26" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J26" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1326,25 +1326,25 @@
         <v>233</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F27" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G27" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I27" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J27" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1361,25 +1361,25 @@
         <v>233</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F28" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I28" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J28" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1396,25 +1396,25 @@
         <v>233</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F29" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I29" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J29" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1431,25 +1431,25 @@
         <v>233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F30" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I30" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J30" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1466,25 +1466,25 @@
         <v>233</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F31" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G31" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I31" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J31" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1501,25 +1501,25 @@
         <v>233</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F32" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G32" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I32" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J32" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1536,25 +1536,25 @@
         <v>233</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F33" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I33" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J33" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1571,25 +1571,25 @@
         <v>233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F34" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I34" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1606,25 +1606,25 @@
         <v>233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F35" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G35" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I35" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J35" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1641,25 +1641,25 @@
         <v>233</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F36" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I36" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J36" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1676,25 +1676,25 @@
         <v>233</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F37" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G37" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I37" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J37" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1711,25 +1711,25 @@
         <v>233</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F38" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I38" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J38" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1746,25 +1746,25 @@
         <v>233</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E39" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F39" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G39" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I39" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J39" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1781,25 +1781,25 @@
         <v>233</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F40" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I40" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J40" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1816,25 +1816,25 @@
         <v>233</v>
       </c>
       <c r="D41" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F41" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G41" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I41" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J41" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1851,25 +1851,25 @@
         <v>233</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F42" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G42" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I42" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J42" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1886,25 +1886,25 @@
         <v>233</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F43" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G43" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I43" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J43" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1921,25 +1921,25 @@
         <v>233</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F44" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G44" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I44" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J44" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1956,25 +1956,25 @@
         <v>233</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E45" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F45" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G45" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I45" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J45" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -1991,25 +1991,25 @@
         <v>233</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F46" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G46" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I46" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J46" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2026,25 +2026,25 @@
         <v>233</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F47" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G47" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I47" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J47" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2061,25 +2061,25 @@
         <v>233</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F48" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G48" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I48" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J48" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2096,25 +2096,25 @@
         <v>233</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01913364870431505</v>
+        <v>0.03494176044427086</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01488747402338131</v>
+        <v>0.03076401914749283</v>
       </c>
       <c r="F49" t="n">
-        <v>4.506090809271114</v>
+        <v>8.363792289201486</v>
       </c>
       <c r="G49" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>2.026348644764353</v>
+        <v>213.860861192194</v>
       </c>
       <c r="I49" t="n">
-        <v>105.9049779829692</v>
+        <v>6120.49474534301</v>
       </c>
       <c r="J49" t="n">
-        <v>0.008734261399846356</v>
+        <v>0.9218140568629059</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,24 +491,28 @@
         <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G2" t="n">
-        <v>0.001</v>
+        <v>0.366</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I2" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="3">
@@ -522,24 +526,28 @@
         <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G3" t="n">
-        <v>0.001</v>
+        <v>0.339</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I3" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="4">
@@ -553,24 +561,28 @@
         <v>57</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G4" t="n">
-        <v>0.001</v>
+        <v>0.363</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I4" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="5">
@@ -584,24 +596,28 @@
         <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G5" t="n">
-        <v>0.001</v>
+        <v>0.374</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I5" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="6">
@@ -615,24 +631,28 @@
         <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G6" t="n">
-        <v>0.001</v>
+        <v>0.352</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I6" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="7">
@@ -646,24 +666,28 @@
         <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.349</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I7" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="8">
@@ -677,24 +701,28 @@
         <v>57</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.355</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I8" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="9">
@@ -708,24 +736,28 @@
         <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.374</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I9" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="10">
@@ -739,24 +771,28 @@
         <v>57</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G10" t="n">
-        <v>0.001</v>
+        <v>0.366</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I10" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="11">
@@ -770,24 +806,28 @@
         <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.09486046556535253</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0.006121295522739989</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.068980761481098</v>
+      </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.377</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>113.2402726323594</v>
       </c>
       <c r="I11" t="n">
         <v>1193.756239308613</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.8587878016819933</v>
+      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>16.05323832208607</v>
       </c>
     </row>
     <row r="12">
@@ -801,28 +841,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02269091255701996</v>
+        <v>0.09273371658976785</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005238964566966819</v>
+        <v>0.005496573954168471</v>
       </c>
       <c r="F12" t="n">
-        <v>1.300193684392866</v>
+        <v>1.063007267181234</v>
       </c>
       <c r="G12" t="n">
-        <v>0.23</v>
+        <v>0.355</v>
       </c>
       <c r="H12" t="n">
-        <v>27.71632719738638</v>
+        <v>113.2716908045437</v>
       </c>
       <c r="I12" t="n">
         <v>1221.472566506</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4862513543401121</v>
+        <v>0.8415333190615926</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>16.43949747034235</v>
       </c>
     </row>
     <row r="13">
@@ -836,28 +876,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02453033892644999</v>
+        <v>0.09461197743272624</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008272511241890879</v>
+        <v>0.01377376113207684</v>
       </c>
       <c r="F13" t="n">
-        <v>1.50883250840133</v>
+        <v>1.170386752236716</v>
       </c>
       <c r="G13" t="n">
-        <v>0.126</v>
+        <v>0.213</v>
       </c>
       <c r="H13" t="n">
-        <v>32.45789024453138</v>
+        <v>125.1880452421424</v>
       </c>
       <c r="I13" t="n">
         <v>1323.17333004859</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5320965613857604</v>
+        <v>0.7706659272543467</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>17.04541693731259</v>
       </c>
     </row>
     <row r="14">
@@ -871,28 +911,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01620875000947223</v>
+        <v>0.09124306910617572</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001073500009617923</v>
+        <v>0.01675479608209174</v>
       </c>
       <c r="F14" t="n">
-        <v>1.070927140921246</v>
+        <v>1.224931998043162</v>
       </c>
       <c r="G14" t="n">
-        <v>0.351</v>
+        <v>0.163</v>
       </c>
       <c r="H14" t="n">
-        <v>23.367298642189</v>
+        <v>131.540312706897</v>
       </c>
       <c r="I14" t="n">
         <v>1441.647173812502</v>
       </c>
       <c r="J14" t="n">
-        <v>0.354049979427106</v>
+        <v>0.7924681245655415</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>16.13716869647616</v>
       </c>
     </row>
     <row r="15">
@@ -906,28 +946,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01460547295425601</v>
+        <v>0.08607162238681054</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005284082821739311</v>
+        <v>0.01683462408278114</v>
       </c>
       <c r="F15" t="n">
-        <v>1.037536822802406</v>
+        <v>1.243144915220874</v>
       </c>
       <c r="G15" t="n">
-        <v>0.349</v>
+        <v>0.16</v>
       </c>
       <c r="H15" t="n">
-        <v>22.56871389911598</v>
+        <v>132.9998574208872</v>
       </c>
       <c r="I15" t="n">
         <v>1545.223079718175</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3178692098467041</v>
+        <v>0.7639330538564986</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>17.19867257881291</v>
       </c>
     </row>
     <row r="16">
@@ -941,28 +981,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01247551195550653</v>
+        <v>0.08367076427450235</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0008694135586082563</v>
+        <v>0.01821867600839544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9348506248544681</v>
+        <v>1.278351332876105</v>
       </c>
       <c r="G16" t="n">
-        <v>0.468</v>
+        <v>0.135</v>
       </c>
       <c r="H16" t="n">
-        <v>20.33865913189402</v>
+        <v>136.4073201928221</v>
       </c>
       <c r="I16" t="n">
         <v>1630.286532883871</v>
       </c>
       <c r="J16" t="n">
-        <v>0.271182121758587</v>
+        <v>0.8156189763234923</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>17.57972441155299</v>
       </c>
     </row>
     <row r="17">
@@ -976,28 +1016,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01650073871402433</v>
+        <v>0.09339040005370247</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004051380976227148</v>
+        <v>0.03294976005728267</v>
       </c>
       <c r="F17" t="n">
-        <v>1.325428914611946</v>
+        <v>1.545159019812404</v>
       </c>
       <c r="G17" t="n">
-        <v>0.205</v>
+        <v>0.019</v>
       </c>
       <c r="H17" t="n">
-        <v>28.33363958879021</v>
+        <v>160.3619075505736</v>
       </c>
       <c r="I17" t="n">
         <v>1717.113402002351</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3541704948598777</v>
+        <v>0.9613373341215894</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>20.63707056100617</v>
       </c>
     </row>
     <row r="18">
@@ -1011,28 +1051,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01372764539297056</v>
+        <v>0.09373505684960622</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001986307838125034</v>
+        <v>0.03709349790270666</v>
       </c>
       <c r="F18" t="n">
-        <v>1.169172194296146</v>
+        <v>1.654881302569392</v>
       </c>
       <c r="G18" t="n">
-        <v>0.267</v>
+        <v>0.014</v>
       </c>
       <c r="H18" t="n">
-        <v>24.89531983682641</v>
+        <v>169.9901296539163</v>
       </c>
       <c r="I18" t="n">
         <v>1813.517112670642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2928861157273693</v>
+        <v>0.8604724793907259</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>23.33475827825195</v>
       </c>
     </row>
     <row r="19">
@@ -1046,28 +1086,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01250334781456195</v>
+        <v>0.1045073451699739</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001281794948818304</v>
+        <v>0.05120421095390093</v>
       </c>
       <c r="F19" t="n">
-        <v>1.114226164966108</v>
+        <v>1.960622892198727</v>
       </c>
       <c r="G19" t="n">
-        <v>0.326</v>
+        <v>0.003</v>
       </c>
       <c r="H19" t="n">
-        <v>24.23803397751677</v>
+        <v>202.5899479641603</v>
       </c>
       <c r="I19" t="n">
         <v>1938.523532816395</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2723374604215367</v>
+        <v>0.980813329071342</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>23.04062819040346</v>
       </c>
     </row>
     <row r="20">
@@ -1081,28 +1121,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006237432351329804</v>
+        <v>0.09692062113028689</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.00444818665564517</v>
+        <v>0.04618582456457276</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5837221360090018</v>
+        <v>1.910338223289228</v>
       </c>
       <c r="G20" t="n">
-        <v>0.82</v>
+        <v>0.003</v>
       </c>
       <c r="H20" t="n">
-        <v>12.82406472187948</v>
+        <v>199.2673023531185</v>
       </c>
       <c r="I20" t="n">
         <v>2055.984578196735</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1364262204455263</v>
+        <v>0.9536072016569527</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>25.68298951084523</v>
       </c>
     </row>
     <row r="21">
@@ -1116,28 +1156,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0102538231992958</v>
+        <v>0.09498735177881684</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0001543724156152226</v>
+        <v>0.046848381128754</v>
       </c>
       <c r="F21" t="n">
-        <v>1.015285228763587</v>
+        <v>1.973190338225329</v>
       </c>
       <c r="G21" t="n">
-        <v>0.401</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>21.87719381121574</v>
+        <v>202.6616476693315</v>
       </c>
       <c r="I21" t="n">
         <v>2133.564562798214</v>
       </c>
       <c r="J21" t="n">
-        <v>0.220981755668846</v>
+        <v>0.8767115730616204</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>26.17257829096286</v>
       </c>
     </row>
     <row r="22">
@@ -1151,25 +1191,25 @@
         <v>233</v>
       </c>
       <c r="D22" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F22" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I22" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1186,25 +1226,25 @@
         <v>233</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F23" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I23" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1221,25 +1261,25 @@
         <v>233</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F24" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I24" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1256,25 +1296,25 @@
         <v>233</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F25" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I25" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1291,25 +1331,25 @@
         <v>233</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F26" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I26" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1326,25 +1366,25 @@
         <v>233</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E27" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F27" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I27" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1361,25 +1401,25 @@
         <v>233</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E28" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F28" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I28" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1396,25 +1436,25 @@
         <v>233</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F29" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I29" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1431,25 +1471,25 @@
         <v>233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F30" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I30" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1466,25 +1506,25 @@
         <v>233</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F31" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I31" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1501,25 +1541,25 @@
         <v>233</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F32" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I32" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1536,25 +1576,25 @@
         <v>233</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F33" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I33" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1571,25 +1611,25 @@
         <v>233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F34" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I34" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1606,25 +1646,25 @@
         <v>233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F35" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I35" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1641,25 +1681,25 @@
         <v>233</v>
       </c>
       <c r="D36" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F36" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I36" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1676,25 +1716,25 @@
         <v>233</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E37" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F37" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I37" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1711,25 +1751,25 @@
         <v>233</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F38" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I38" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1746,25 +1786,25 @@
         <v>233</v>
       </c>
       <c r="D39" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E39" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F39" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I39" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1781,25 +1821,25 @@
         <v>233</v>
       </c>
       <c r="D40" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F40" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I40" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J40" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1816,25 +1856,25 @@
         <v>233</v>
       </c>
       <c r="D41" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F41" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I41" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1851,25 +1891,25 @@
         <v>233</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E42" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F42" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I42" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1886,25 +1926,25 @@
         <v>233</v>
       </c>
       <c r="D43" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F43" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I43" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1921,25 +1961,25 @@
         <v>233</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F44" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I44" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1956,25 +1996,25 @@
         <v>233</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F45" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I45" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -1991,25 +2031,25 @@
         <v>233</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F46" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I46" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2026,25 +2066,25 @@
         <v>233</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E47" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F47" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I47" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2061,25 +2101,25 @@
         <v>233</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E48" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F48" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I48" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2096,25 +2136,25 @@
         <v>233</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03494176044427086</v>
+        <v>0.1014110673239307</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03076401914749283</v>
+        <v>0.08161835955573538</v>
       </c>
       <c r="F49" t="n">
-        <v>8.363792289201486</v>
+        <v>5.123658092243791</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>213.860861192194</v>
+        <v>620.685904675744</v>
       </c>
       <c r="I49" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9218140568629059</v>
+        <v>1.574534992213807</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -488,31 +488,31 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F2" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G2" t="n">
-        <v>0.366</v>
+        <v>0.001</v>
       </c>
       <c r="H2" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I2" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K2" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +523,31 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F3" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.339</v>
+        <v>0.001</v>
       </c>
       <c r="H3" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I3" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K3" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F4" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G4" t="n">
-        <v>0.363</v>
+        <v>0.001</v>
       </c>
       <c r="H4" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I4" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K4" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F5" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G5" t="n">
-        <v>0.374</v>
+        <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I5" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K5" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F6" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G6" t="n">
-        <v>0.352</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I6" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K6" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F7" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G7" t="n">
-        <v>0.349</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I7" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K7" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F8" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G8" t="n">
-        <v>0.355</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I8" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K8" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F9" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.374</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I9" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K9" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F10" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G10" t="n">
-        <v>0.366</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I10" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K10" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>0.09486046556535253</v>
+        <v>0.2059772426470385</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006121295522739989</v>
+        <v>0.1467218129938325</v>
       </c>
       <c r="F11" t="n">
-        <v>1.068980761481098</v>
+        <v>3.476090610641514</v>
       </c>
       <c r="G11" t="n">
-        <v>0.377</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>113.2402726323594</v>
+        <v>381.4027242004413</v>
       </c>
       <c r="I11" t="n">
-        <v>1193.756239308613</v>
+        <v>1851.674094181419</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8587878016819933</v>
+        <v>4.098282586189645</v>
       </c>
       <c r="K11" t="n">
-        <v>16.05323832208607</v>
+        <v>3.257428671522138</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09273371658976785</v>
+        <v>0.1879770547861894</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005496573954168471</v>
+        <v>0.1307923403345127</v>
       </c>
       <c r="F12" t="n">
-        <v>1.063007267181234</v>
+        <v>3.287190582109786</v>
       </c>
       <c r="G12" t="n">
-        <v>0.355</v>
+        <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>113.2716908045437</v>
+        <v>365.1706141008648</v>
       </c>
       <c r="I12" t="n">
-        <v>1221.472566506</v>
+        <v>1942.633980068581</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8415333190615926</v>
+        <v>3.668079660838305</v>
       </c>
       <c r="K12" t="n">
-        <v>16.43949747034235</v>
+        <v>3.427863304970906</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.09461197743272624</v>
+        <v>0.1895609603152558</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01377376113207684</v>
+        <v>0.1369350486474152</v>
       </c>
       <c r="F13" t="n">
-        <v>1.170386752236716</v>
+        <v>3.602046108231046</v>
       </c>
       <c r="G13" t="n">
-        <v>0.213</v>
+        <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>125.1880452421424</v>
+        <v>398.1879144980711</v>
       </c>
       <c r="I13" t="n">
-        <v>1323.17333004859</v>
+        <v>2100.579749310466</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7706659272543467</v>
+        <v>3.671719855765078</v>
       </c>
       <c r="K13" t="n">
-        <v>17.04541693731259</v>
+        <v>3.148523905387103</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09124306910617572</v>
+        <v>0.1723141820514099</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01675479608209174</v>
+        <v>0.1224535906087236</v>
       </c>
       <c r="F14" t="n">
-        <v>1.224931998043162</v>
+        <v>3.455919335603586</v>
       </c>
       <c r="G14" t="n">
-        <v>0.163</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>131.540312706897</v>
+        <v>388.0327834197182</v>
       </c>
       <c r="I14" t="n">
-        <v>1441.647173812502</v>
+        <v>2251.89116067039</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7924681245655415</v>
+        <v>3.317540845574616</v>
       </c>
       <c r="K14" t="n">
-        <v>16.13716869647616</v>
+        <v>3.328515319583292</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08607162238681054</v>
+        <v>0.1713530624226824</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01683462408278114</v>
+        <v>0.1253171214461648</v>
       </c>
       <c r="F15" t="n">
-        <v>1.243144915220874</v>
+        <v>3.722158356882235</v>
       </c>
       <c r="G15" t="n">
-        <v>0.16</v>
+        <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>132.9998574208872</v>
+        <v>416.0643176057742</v>
       </c>
       <c r="I15" t="n">
-        <v>1545.223079718175</v>
+        <v>2428.111360971502</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7639330538564986</v>
+        <v>3.344082886305435</v>
       </c>
       <c r="K15" t="n">
-        <v>17.19867257881291</v>
+        <v>3.440807935581242</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08367076427450235</v>
+        <v>0.1778821052081558</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01821867600839544</v>
+        <v>0.135063464854414</v>
       </c>
       <c r="F16" t="n">
-        <v>1.278351332876105</v>
+        <v>4.154314656855068</v>
       </c>
       <c r="G16" t="n">
-        <v>0.135</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>136.4073201928221</v>
+        <v>457.0325838396894</v>
       </c>
       <c r="I16" t="n">
-        <v>1630.286532883871</v>
+        <v>2569.30051117213</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8156189763234923</v>
+        <v>3.53643361223686</v>
       </c>
       <c r="K16" t="n">
-        <v>17.57972441155299</v>
+        <v>3.590532157936295</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09339040005370247</v>
+        <v>0.1816345347101616</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03294976005728267</v>
+        <v>0.1415185805292872</v>
       </c>
       <c r="F17" t="n">
-        <v>1.545159019812404</v>
+        <v>4.527738113649487</v>
       </c>
       <c r="G17" t="n">
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>160.3619075505736</v>
+        <v>497.1237539218122</v>
       </c>
       <c r="I17" t="n">
-        <v>1717.113402002351</v>
+        <v>2736.945122881416</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9613373341215894</v>
+        <v>3.571490106711147</v>
       </c>
       <c r="K17" t="n">
-        <v>20.63707056100617</v>
+        <v>3.730483117207455</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09373505684960622</v>
+        <v>0.1815120186352368</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03709349790270666</v>
+        <v>0.1436190565350163</v>
       </c>
       <c r="F18" t="n">
-        <v>1.654881302569392</v>
+        <v>4.790124829913482</v>
       </c>
       <c r="G18" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>169.9901296539163</v>
+        <v>519.1722281443733</v>
       </c>
       <c r="I18" t="n">
-        <v>1813.517112670642</v>
+        <v>2860.26364561397</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8604724793907259</v>
+        <v>3.403827239368157</v>
       </c>
       <c r="K18" t="n">
-        <v>23.33475827825195</v>
+        <v>3.855027137717347</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1045073451699739</v>
+        <v>0.1745212416838252</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05120421095390093</v>
+        <v>0.1383160329857474</v>
       </c>
       <c r="F19" t="n">
-        <v>1.960622892198727</v>
+        <v>4.820335193733896</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>202.5899479641603</v>
+        <v>519.9667364455968</v>
       </c>
       <c r="I19" t="n">
-        <v>1938.523532816395</v>
+        <v>2979.38939368541</v>
       </c>
       <c r="J19" t="n">
-        <v>0.980813329071342</v>
+        <v>3.204997495329263</v>
       </c>
       <c r="K19" t="n">
-        <v>23.04062819040346</v>
+        <v>3.953936295852069</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09692062113028689</v>
+        <v>0.1770269462939102</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04618582456457276</v>
+        <v>0.1430197953143197</v>
       </c>
       <c r="F20" t="n">
-        <v>1.910338223289228</v>
+        <v>5.205580038155907</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>199.2673023531185</v>
+        <v>555.5491095556861</v>
       </c>
       <c r="I20" t="n">
-        <v>2055.984578196735</v>
+        <v>3138.217775238193</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9536072016569527</v>
+        <v>3.223479395458611</v>
       </c>
       <c r="K20" t="n">
-        <v>25.68298951084523</v>
+        <v>3.606020413782225</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09498735177881684</v>
+        <v>0.1671951700237239</v>
       </c>
       <c r="E21" t="n">
-        <v>0.046848381128754</v>
+        <v>0.1344075782923746</v>
       </c>
       <c r="F21" t="n">
-        <v>1.973190338225329</v>
+        <v>5.099342806073259</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>202.6616476693315</v>
+        <v>557.963480535009</v>
       </c>
       <c r="I21" t="n">
-        <v>2133.564562798214</v>
+        <v>3337.198559359325</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8767115730616204</v>
+        <v>3.13149463621279</v>
       </c>
       <c r="K21" t="n">
-        <v>26.17257829096286</v>
+        <v>3.830513814545031</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1653376034645286</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1339593178804882</v>
       </c>
       <c r="F22" t="n">
-        <v>5.123658092243791</v>
+        <v>5.269172626455509</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>620.685904675744</v>
+        <v>565.0338114029144</v>
       </c>
       <c r="I22" t="n">
-        <v>6120.49474534301</v>
+        <v>3417.454950132602</v>
       </c>
       <c r="J22" t="n">
-        <v>1.574534992213807</v>
+        <v>3.004821897171264</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>3.808328218021247</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1595885382031379</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1293579100809487</v>
       </c>
       <c r="F23" t="n">
-        <v>5.123658092243791</v>
+        <v>5.279034810593296</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>620.685904675744</v>
+        <v>560.292697363376</v>
       </c>
       <c r="I23" t="n">
-        <v>6120.49474534301</v>
+        <v>3510.85800817467</v>
       </c>
       <c r="J23" t="n">
-        <v>1.574534992213807</v>
+        <v>2.74478706296467</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>4.08419358166231</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>233</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1609592739334942</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1320268351036146</v>
       </c>
       <c r="F24" t="n">
-        <v>5.123658092243791</v>
+        <v>5.56328054056978</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>620.685904675744</v>
+        <v>584.0607510682651</v>
       </c>
       <c r="I24" t="n">
-        <v>6120.49474534301</v>
+        <v>3628.624414083713</v>
       </c>
       <c r="J24" t="n">
-        <v>1.574534992213807</v>
+        <v>2.646026079979103</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>4.16835008382468</v>
       </c>
     </row>
     <row r="25">
@@ -1293,28 +1293,28 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F25" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I25" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J25" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1328,28 +1328,28 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F26" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I26" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J26" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1363,28 +1363,28 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E27" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F27" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I27" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J27" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -1398,28 +1398,28 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F28" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I28" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J28" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1433,28 +1433,28 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F29" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I29" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J29" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -1468,28 +1468,28 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F30" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I30" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J30" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1503,28 +1503,28 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F31" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I31" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J31" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1538,28 +1538,28 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E32" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F32" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I32" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J32" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -1573,28 +1573,28 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E33" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F33" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I33" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J33" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -1608,28 +1608,28 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F34" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I34" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J34" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -1643,28 +1643,28 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F35" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I35" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J35" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1678,28 +1678,28 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F36" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I36" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J36" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -1713,28 +1713,28 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F37" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I37" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J37" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -1748,28 +1748,28 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E38" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F38" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I38" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J38" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1783,28 +1783,28 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E39" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F39" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I39" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J39" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -1818,28 +1818,28 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F40" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I40" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J40" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E41" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F41" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I41" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J41" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -1888,28 +1888,28 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E42" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F42" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I42" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J42" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -1923,28 +1923,28 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E43" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F43" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I43" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J43" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -1958,28 +1958,28 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F44" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I44" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J44" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -1993,28 +1993,28 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E45" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F45" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I45" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J45" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -2028,28 +2028,28 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E46" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F46" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I46" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J46" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -2063,28 +2063,28 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F47" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I47" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J47" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -2098,28 +2098,28 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E48" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F48" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I48" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J48" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2133,28 +2133,28 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1014110673239307</v>
+        <v>0.1342517402857852</v>
       </c>
       <c r="E49" t="n">
-        <v>0.08161835955573538</v>
+        <v>0.1200124596983804</v>
       </c>
       <c r="F49" t="n">
-        <v>5.123658092243791</v>
+        <v>9.428267071619871</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>620.685904675744</v>
+        <v>1128.927414843839</v>
       </c>
       <c r="I49" t="n">
-        <v>6120.49474534301</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J49" t="n">
-        <v>1.574534992213807</v>
+        <v>2.028026433586267</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>

--- a/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/HZD_Focus/tables/stressor_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F2" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G2" t="n">
         <v>0.001</v>
       </c>
       <c r="H2" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I2" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J2" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K2" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>73</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F3" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G3" t="n">
         <v>0.001</v>
       </c>
       <c r="H3" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I3" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J3" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K3" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>73</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F4" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G4" t="n">
         <v>0.001</v>
       </c>
       <c r="H4" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I4" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J4" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K4" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>73</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F5" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G5" t="n">
         <v>0.001</v>
       </c>
       <c r="H5" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I5" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J5" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K5" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F6" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G6" t="n">
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I6" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J6" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K6" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>73</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G7" t="n">
         <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I7" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J7" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K7" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>73</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F8" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G8" t="n">
         <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I8" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J8" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K8" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F9" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I9" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J9" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K9" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>73</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F10" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I10" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J10" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K10" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2059772426470385</v>
+        <v>0.2059772426470382</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1467218129938325</v>
+        <v>0.1467218129938321</v>
       </c>
       <c r="F11" t="n">
-        <v>3.476090610641514</v>
+        <v>3.476090610641509</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>381.4027242004413</v>
+        <v>381.4027242004407</v>
       </c>
       <c r="I11" t="n">
         <v>1851.674094181419</v>
       </c>
       <c r="J11" t="n">
-        <v>4.098282586189645</v>
+        <v>4.098282586189635</v>
       </c>
       <c r="K11" t="n">
-        <v>3.257428671522138</v>
+        <v>7.618053298098457</v>
       </c>
     </row>
     <row r="12">
@@ -853,16 +853,16 @@
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>365.1706141008648</v>
+        <v>365.1706141008647</v>
       </c>
       <c r="I12" t="n">
         <v>1942.633980068581</v>
       </c>
       <c r="J12" t="n">
-        <v>3.668079660838305</v>
+        <v>3.668079660838304</v>
       </c>
       <c r="K12" t="n">
-        <v>3.427863304970906</v>
+        <v>8.34917488483414</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1895609603152558</v>
+        <v>0.1895609603152557</v>
       </c>
       <c r="E13" t="n">
         <v>0.1369350486474152</v>
       </c>
       <c r="F13" t="n">
-        <v>3.602046108231046</v>
+        <v>3.602046108231044</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>398.1879144980711</v>
+        <v>398.1879144980709</v>
       </c>
       <c r="I13" t="n">
         <v>2100.579749310466</v>
       </c>
       <c r="J13" t="n">
-        <v>3.671719855765078</v>
+        <v>3.67171985576508</v>
       </c>
       <c r="K13" t="n">
-        <v>3.148523905387103</v>
+        <v>6.651354131394607</v>
       </c>
     </row>
     <row r="14">
@@ -911,7 +911,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1723141820514099</v>
+        <v>0.1723141820514098</v>
       </c>
       <c r="E14" t="n">
         <v>0.1224535906087236</v>
@@ -923,16 +923,16 @@
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>388.0327834197182</v>
+        <v>388.032783419718</v>
       </c>
       <c r="I14" t="n">
         <v>2251.89116067039</v>
       </c>
       <c r="J14" t="n">
-        <v>3.317540845574616</v>
+        <v>3.317540845574614</v>
       </c>
       <c r="K14" t="n">
-        <v>3.328515319583292</v>
+        <v>6.899563435338715</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1713530624226824</v>
+        <v>0.1713530624226826</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1253171214461648</v>
+        <v>0.1253171214461649</v>
       </c>
       <c r="F15" t="n">
-        <v>3.722158356882235</v>
+        <v>3.722158356882237</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>416.0643176057742</v>
+        <v>416.0643176057745</v>
       </c>
       <c r="I15" t="n">
         <v>2428.111360971502</v>
       </c>
       <c r="J15" t="n">
-        <v>3.344082886305435</v>
+        <v>3.344082886305437</v>
       </c>
       <c r="K15" t="n">
-        <v>3.440807935581242</v>
+        <v>7.062161287368077</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1778821052081558</v>
+        <v>0.1778821052081557</v>
       </c>
       <c r="E16" t="n">
-        <v>0.135063464854414</v>
+        <v>0.1350634648544139</v>
       </c>
       <c r="F16" t="n">
-        <v>4.154314656855068</v>
+        <v>4.154314656855065</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>457.0325838396894</v>
+        <v>457.0325838396891</v>
       </c>
       <c r="I16" t="n">
         <v>2569.30051117213</v>
       </c>
       <c r="J16" t="n">
-        <v>3.53643361223686</v>
+        <v>3.536433612236856</v>
       </c>
       <c r="K16" t="n">
-        <v>3.590532157936295</v>
+        <v>7.088105405133867</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1816345347101616</v>
+        <v>0.1816345347101615</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1415185805292872</v>
+        <v>0.141518580529287</v>
       </c>
       <c r="F17" t="n">
-        <v>4.527738113649487</v>
+        <v>4.527738113649484</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>497.1237539218122</v>
+        <v>497.1237539218117</v>
       </c>
       <c r="I17" t="n">
         <v>2736.945122881416</v>
       </c>
       <c r="J17" t="n">
-        <v>3.571490106711147</v>
+        <v>3.571490106711145</v>
       </c>
       <c r="K17" t="n">
-        <v>3.730483117207455</v>
+        <v>7.396026412518752</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1815120186352368</v>
+        <v>0.1815120186352366</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1436190565350163</v>
+        <v>0.1436190565350161</v>
       </c>
       <c r="F18" t="n">
-        <v>4.790124829913482</v>
+        <v>4.790124829913474</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>519.1722281443733</v>
+        <v>519.1722281443725</v>
       </c>
       <c r="I18" t="n">
         <v>2860.26364561397</v>
       </c>
       <c r="J18" t="n">
-        <v>3.403827239368157</v>
+        <v>3.403827239368145</v>
       </c>
       <c r="K18" t="n">
-        <v>3.855027137717347</v>
+        <v>7.302291552842163</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1745212416838252</v>
+        <v>0.1745212416838254</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1383160329857474</v>
+        <v>0.1383160329857476</v>
       </c>
       <c r="F19" t="n">
-        <v>4.820335193733896</v>
+        <v>4.820335193733901</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>519.9667364455968</v>
+        <v>519.9667364455973</v>
       </c>
       <c r="I19" t="n">
         <v>2979.38939368541</v>
       </c>
       <c r="J19" t="n">
-        <v>3.204997495329263</v>
+        <v>3.204997495329267</v>
       </c>
       <c r="K19" t="n">
-        <v>3.953936295852069</v>
+        <v>7.618825632005373</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1770269462939102</v>
+        <v>0.1770269462939107</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1430197953143197</v>
+        <v>0.1430197953143202</v>
       </c>
       <c r="F20" t="n">
-        <v>5.205580038155907</v>
+        <v>5.205580038155918</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>555.5491095556861</v>
+        <v>555.5491095556873</v>
       </c>
       <c r="I20" t="n">
         <v>3138.217775238193</v>
       </c>
       <c r="J20" t="n">
-        <v>3.223479395458611</v>
+        <v>3.223479395458619</v>
       </c>
       <c r="K20" t="n">
-        <v>3.606020413782225</v>
+        <v>6.396613824988021</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1671951700237239</v>
+        <v>0.1671951700237238</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1344075782923746</v>
+        <v>0.1344075782923745</v>
       </c>
       <c r="F21" t="n">
-        <v>5.099342806073259</v>
+        <v>5.099342806073256</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>557.963480535009</v>
+        <v>557.9634805350087</v>
       </c>
       <c r="I21" t="n">
         <v>3337.198559359325</v>
       </c>
       <c r="J21" t="n">
-        <v>3.13149463621279</v>
+        <v>3.131494636212788</v>
       </c>
       <c r="K21" t="n">
-        <v>3.830513814545031</v>
+        <v>6.318823769436523</v>
       </c>
     </row>
     <row r="22">
@@ -1194,25 +1194,25 @@
         <v>0.1653376034645286</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1339593178804882</v>
+        <v>0.1339593178804883</v>
       </c>
       <c r="F22" t="n">
-        <v>5.269172626455509</v>
+        <v>5.26917262645551</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>565.0338114029144</v>
+        <v>565.0338114029145</v>
       </c>
       <c r="I22" t="n">
         <v>3417.454950132602</v>
       </c>
       <c r="J22" t="n">
-        <v>3.004821897171264</v>
+        <v>3.004821897171262</v>
       </c>
       <c r="K22" t="n">
-        <v>3.808328218021247</v>
+        <v>6.983521941156175</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1595885382031379</v>
+        <v>0.1595885382031378</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1293579100809487</v>
+        <v>0.1293579100809485</v>
       </c>
       <c r="F23" t="n">
-        <v>5.279034810593296</v>
+        <v>5.279034810593294</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>560.292697363376</v>
+        <v>560.2926973633757</v>
       </c>
       <c r="I23" t="n">
         <v>3510.85800817467</v>
       </c>
       <c r="J23" t="n">
-        <v>2.74478706296467</v>
+        <v>2.744787062964669</v>
       </c>
       <c r="K23" t="n">
-        <v>4.08419358166231</v>
+        <v>7.1407644224968</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1609592739334942</v>
+        <v>0.160959273933494</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1320268351036146</v>
+        <v>0.1320268351036143</v>
       </c>
       <c r="F24" t="n">
-        <v>5.56328054056978</v>
+        <v>5.563280540569773</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>584.0607510682651</v>
+        <v>584.0607510682644</v>
       </c>
       <c r="I24" t="n">
         <v>3628.624414083713</v>
       </c>
       <c r="J24" t="n">
-        <v>2.646026079979103</v>
+        <v>2.646026079979099</v>
       </c>
       <c r="K24" t="n">
-        <v>4.16835008382468</v>
+        <v>7.171217634077469</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>310</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F25" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I25" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J25" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>310</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F26" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I26" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J26" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>310</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F27" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I27" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J27" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>310</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F28" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I28" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J28" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>310</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F29" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I29" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J29" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>310</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F30" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I30" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J30" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>310</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F31" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I31" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J31" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>310</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F32" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I32" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J32" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>310</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F33" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I33" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J33" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>310</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F34" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I34" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J34" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>310</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F35" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I35" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J35" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>310</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F36" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I36" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J36" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>310</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F37" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I37" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J37" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>310</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F38" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I38" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J38" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>310</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F39" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I39" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J39" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>310</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F40" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I40" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J40" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>310</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F41" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I41" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J41" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>310</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F42" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I42" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J42" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>310</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F43" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I43" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J43" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>310</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F44" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I44" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J44" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>310</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F45" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I45" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J45" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>310</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F46" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I46" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J46" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>310</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F47" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I47" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J47" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>310</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F48" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I48" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J48" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
     <row r="49">
@@ -2136,28 +2136,28 @@
         <v>310</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1342517402857852</v>
+        <v>0.1342517402857851</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1200124596983804</v>
+        <v>0.1200124596983803</v>
       </c>
       <c r="F49" t="n">
-        <v>9.428267071619871</v>
+        <v>9.428267071619864</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1128.927414843839</v>
+        <v>1128.927414843838</v>
       </c>
       <c r="I49" t="n">
         <v>8409.033748394333</v>
       </c>
       <c r="J49" t="n">
-        <v>2.028026433586267</v>
+        <v>2.028026433586264</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>1.785247080128419</v>
       </c>
     </row>
   </sheetData>
